--- a/xll_placket.xlsx
+++ b/xll_placket.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\keith\source\repos\xlladdins\xll_plackett\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AE730BE-C486-48DE-8B6F-A8410AF31C1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAED38C4-C731-426B-8D58-36EDF0AD0279}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="22276" windowHeight="13996" xr2:uid="{AB3A62A4-5861-49CD-9E41-6EE096DB294B}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="theta">Sheet1!$C$3</definedName>
+    <definedName name="theta">Sheet1!$C$2</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,6 +41,28 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1" uniqueCount="1">
   <si>
@@ -51,10 +73,20 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="&quot;0x&quot;#"/>
+  </numFmts>
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="14"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color indexed="63"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -77,8 +109,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -86,11 +121,80 @@
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Handle" xfId="1" xr:uid="{4E7C6F6C-7AB9-43C9-9EF4-A7308A837550}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00FF0000"/>
+    </indexedColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -100,6 +204,3597 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:view3D>
+      <c:rotX val="15"/>
+      <c:rotY val="20"/>
+      <c:rAngAx val="0"/>
+    </c:view3D>
+    <c:floor>
+      <c:thickness val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+        <a:sp3d/>
+      </c:spPr>
+    </c:floor>
+    <c:sideWall>
+      <c:thickness val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+        <a:sp3d/>
+      </c:spPr>
+    </c:sideWall>
+    <c:backWall>
+      <c:thickness val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+        <a:sp3d/>
+      </c:spPr>
+    </c:backWall>
+    <c:plotArea>
+      <c:layout/>
+      <c:surface3DChart>
+        <c:wireframe val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$C$17</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln/>
+            <a:effectLst/>
+            <a:sp3d/>
+          </c:spPr>
+          <c:cat>
+            <c:numRef>
+              <c:f>Sheet1!$D$16:$N$16</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.4</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.6</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.7</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.8</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.9</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$D$17:$N$17</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>1E-3</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.2342935985300352E-3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.5617190428711242E-3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2.0390681792827859E-3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2.7740777744883374E-3</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>3.9920119840199777E-3</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>6.2312921032829172E-3</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1.105944017777386E-2</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2.4801193631847115E-2</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>9.8224011645438827E-2</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>999.99999999999829</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-B9BF-43E4-BE33-1A4A56B371B3}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$C$18</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>0.1</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln/>
+            <a:effectLst/>
+            <a:sp3d/>
+          </c:spPr>
+          <c:cat>
+            <c:numRef>
+              <c:f>Sheet1!$D$16:$N$16</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.4</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.6</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.7</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.8</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.9</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$D$18:$N$18</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>1.2342935985300352E-3</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.6005633972407799E-3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2.1548932066352512E-3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3.0495021897984347E-3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4.6250302965488033E-3</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>7.7707099460882492E-3</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1.5407183256802326E-2</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>4.1641495228951074E-2</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.24232226107297336</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>26.401926844269422</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>9.8224011645438758E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-B9BF-43E4-BE33-1A4A56B371B3}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$C$19</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>0.2</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent3"/>
+            </a:solidFill>
+            <a:ln/>
+            <a:effectLst/>
+            <a:sp3d/>
+          </c:spPr>
+          <c:cat>
+            <c:numRef>
+              <c:f>Sheet1!$D$16:$N$16</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.4</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.6</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.7</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.8</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.9</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$D$19:$N$19</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>1.5617190428711242E-3</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2.1548932066352512E-3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3.141249243121604E-3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4.9410850590055049E-3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>8.6916032918170089E-3</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1.828652524625822E-2</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>5.3457945533076284E-2</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.34195583529660456</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>19.789534608545942</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.24232226107297336</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2.4801193631847174E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-B9BF-43E4-BE33-1A4A56B371B3}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$C$20</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>0.3</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent4"/>
+            </a:solidFill>
+            <a:ln/>
+            <a:effectLst/>
+            <a:sp3d/>
+          </c:spPr>
+          <c:cat>
+            <c:numRef>
+              <c:f>Sheet1!$D$16:$N$16</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.4</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.6</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.7</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.8</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.9</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$D$20:$N$20</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>2.0390681792827859E-3</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3.0495021897984347E-3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4.9410850590055049E-3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>8.9981094652824591E-3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.9720488121697521E-2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6.0464436173095923E-2</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.40468977437845532</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>17.270528003950261</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.3419558352966055</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>4.1641495228951206E-2</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1.1059440177773869E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-B9BF-43E4-BE33-1A4A56B371B3}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="4"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$C$21</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>0.4</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent5"/>
+            </a:solidFill>
+            <a:ln/>
+            <a:effectLst/>
+            <a:sp3d/>
+          </c:spPr>
+          <c:cat>
+            <c:numRef>
+              <c:f>Sheet1!$D$16:$N$16</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.4</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.6</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.7</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.8</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.9</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$D$21:$N$21</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>2.7740777744883374E-3</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4.6250302965488033E-3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>8.6916032918170089E-3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.9720488121697521E-2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>6.2786189138963278E-2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.43501073894100922</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>16.153903196224309</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.40468977437845638</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>5.3457945533076208E-2</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1.5407183256802345E-2</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>6.2312921032829285E-3</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000004-B9BF-43E4-BE33-1A4A56B371B3}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="5"/>
+          <c:order val="5"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$C$22</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>0.5</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent6"/>
+            </a:solidFill>
+            <a:ln/>
+            <a:effectLst/>
+            <a:sp3d/>
+          </c:spPr>
+          <c:cat>
+            <c:numRef>
+              <c:f>Sheet1!$D$16:$N$16</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.4</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.6</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.7</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.8</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.9</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$D$22:$N$22</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>3.9920119840199777E-3</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>7.7707099460882492E-3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.828652524625822E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>6.0464436173095923E-2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.43501073894100922</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>15.827199689142736</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.43501073894100939</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>6.0464436173096006E-2</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1.8286525246258237E-2</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>7.7707099460882639E-3</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>3.9920119840199759E-3</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000005-B9BF-43E4-BE33-1A4A56B371B3}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="6"/>
+          <c:order val="6"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$C$23</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>0.6</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1">
+                <a:lumMod val="60000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln/>
+            <a:effectLst/>
+            <a:sp3d/>
+          </c:spPr>
+          <c:cat>
+            <c:numRef>
+              <c:f>Sheet1!$D$16:$N$16</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.4</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.6</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.7</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.8</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.9</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$D$23:$N$23</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>6.2312921032829172E-3</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.5407183256802326E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>5.3457945533076284E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.40468977437845532</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>16.153903196224309</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.43501073894100939</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>6.2786189138963375E-2</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1.9720488121697591E-2</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>8.6916032918170176E-3</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>4.6250302965488051E-3</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2.7740777744883365E-3</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000006-B9BF-43E4-BE33-1A4A56B371B3}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="7"/>
+          <c:order val="7"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$C$24</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>0.7</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2">
+                <a:lumMod val="60000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln/>
+            <a:effectLst/>
+            <a:sp3d/>
+          </c:spPr>
+          <c:cat>
+            <c:numRef>
+              <c:f>Sheet1!$D$16:$N$16</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.4</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.6</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.7</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.8</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.9</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$D$24:$N$24</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>1.105944017777386E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4.1641495228951074E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.34195583529660456</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>17.270528003950261</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.40468977437845638</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6.0464436173096006E-2</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1.9720488121697591E-2</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8.9981094652824747E-3</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>4.9410850590055041E-3</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>3.0495021897984347E-3</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2.0390681792827863E-3</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000007-B9BF-43E4-BE33-1A4A56B371B3}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="8"/>
+          <c:order val="8"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$C$25</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>0.8</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent3">
+                <a:lumMod val="60000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln/>
+            <a:effectLst/>
+            <a:sp3d/>
+          </c:spPr>
+          <c:cat>
+            <c:numRef>
+              <c:f>Sheet1!$D$16:$N$16</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.4</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.6</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.7</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.8</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.9</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$D$25:$N$25</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>2.4801193631847115E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.24232226107297336</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>19.789534608545942</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.3419558352966055</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5.3457945533076208E-2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1.8286525246258237E-2</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>8.6916032918170176E-3</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>4.9410850590055041E-3</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>3.1412492431216045E-3</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2.1548932066352494E-3</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1.5617190428711244E-3</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000008-B9BF-43E4-BE33-1A4A56B371B3}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="9"/>
+          <c:order val="9"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$C$26</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>0.9</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent4">
+                <a:lumMod val="60000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln/>
+            <a:effectLst/>
+            <a:sp3d/>
+          </c:spPr>
+          <c:cat>
+            <c:numRef>
+              <c:f>Sheet1!$D$16:$N$16</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.4</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.6</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.7</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.8</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.9</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$D$26:$N$26</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>9.8224011645438827E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>26.401926844269422</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.24232226107297336</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4.1641495228951206E-2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.5407183256802345E-2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>7.7707099460882639E-3</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>4.6250302965488051E-3</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>3.0495021897984347E-3</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2.1548932066352494E-3</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1.6005633972407806E-3</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1.2342935985300359E-3</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000009-B9BF-43E4-BE33-1A4A56B371B3}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="10"/>
+          <c:order val="10"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$C$27</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent5">
+                <a:lumMod val="60000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln/>
+            <a:effectLst/>
+            <a:sp3d/>
+          </c:spPr>
+          <c:cat>
+            <c:numRef>
+              <c:f>Sheet1!$D$16:$N$16</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.4</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.6</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.7</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.8</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.9</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$D$27:$N$27</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>999.99999999999829</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>9.8224011645438758E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2.4801193631847174E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.1059440177773869E-2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>6.2312921032829285E-3</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>3.9920119840199759E-3</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2.7740777744883365E-3</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2.0390681792827863E-3</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1.5617190428711244E-3</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1.2342935985300359E-3</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1E-3</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{0000000A-B9BF-43E4-BE33-1A4A56B371B3}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:bandFmts>
+          <c:bandFmt>
+            <c:idx val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln/>
+              <a:effectLst/>
+              <a:sp3d/>
+            </c:spPr>
+          </c:bandFmt>
+          <c:bandFmt>
+            <c:idx val="1"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln/>
+              <a:effectLst/>
+              <a:sp3d/>
+            </c:spPr>
+          </c:bandFmt>
+          <c:bandFmt>
+            <c:idx val="2"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln/>
+              <a:effectLst/>
+              <a:sp3d/>
+            </c:spPr>
+          </c:bandFmt>
+          <c:bandFmt>
+            <c:idx val="3"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:ln/>
+              <a:effectLst/>
+              <a:sp3d/>
+            </c:spPr>
+          </c:bandFmt>
+          <c:bandFmt>
+            <c:idx val="4"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent5"/>
+              </a:solidFill>
+              <a:ln/>
+              <a:effectLst/>
+              <a:sp3d/>
+            </c:spPr>
+          </c:bandFmt>
+          <c:bandFmt>
+            <c:idx val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent6"/>
+              </a:solidFill>
+              <a:ln/>
+              <a:effectLst/>
+              <a:sp3d/>
+            </c:spPr>
+          </c:bandFmt>
+          <c:bandFmt>
+            <c:idx val="6"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln/>
+              <a:effectLst/>
+              <a:sp3d/>
+            </c:spPr>
+          </c:bandFmt>
+          <c:bandFmt>
+            <c:idx val="7"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln/>
+              <a:effectLst/>
+              <a:sp3d/>
+            </c:spPr>
+          </c:bandFmt>
+          <c:bandFmt>
+            <c:idx val="8"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln/>
+              <a:effectLst/>
+              <a:sp3d/>
+            </c:spPr>
+          </c:bandFmt>
+          <c:bandFmt>
+            <c:idx val="9"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln/>
+              <a:effectLst/>
+              <a:sp3d/>
+            </c:spPr>
+          </c:bandFmt>
+          <c:bandFmt>
+            <c:idx val="10"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent5">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln/>
+              <a:effectLst/>
+              <a:sp3d/>
+            </c:spPr>
+          </c:bandFmt>
+          <c:bandFmt>
+            <c:idx val="11"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent6">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln/>
+              <a:effectLst/>
+              <a:sp3d/>
+            </c:spPr>
+          </c:bandFmt>
+          <c:bandFmt>
+            <c:idx val="12"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="80000"/>
+                  <a:lumOff val="20000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln/>
+              <a:effectLst/>
+              <a:sp3d/>
+            </c:spPr>
+          </c:bandFmt>
+          <c:bandFmt>
+            <c:idx val="13"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2">
+                  <a:lumMod val="80000"/>
+                  <a:lumOff val="20000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln/>
+              <a:effectLst/>
+              <a:sp3d/>
+            </c:spPr>
+          </c:bandFmt>
+          <c:bandFmt>
+            <c:idx val="14"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3">
+                  <a:lumMod val="80000"/>
+                  <a:lumOff val="20000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln/>
+              <a:effectLst/>
+              <a:sp3d/>
+            </c:spPr>
+          </c:bandFmt>
+        </c:bandFmts>
+        <c:axId val="1013839487"/>
+        <c:axId val="1013832767"/>
+        <c:axId val="588509023"/>
+      </c:surface3DChart>
+      <c:catAx>
+        <c:axId val="1013839487"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1013832767"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1013832767"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1013839487"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:serAx>
+        <c:axId val="588509023"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1013832767"/>
+        <c:crosses val="autoZero"/>
+      </c:serAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr rtl="0">
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="zero"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:view3D>
+      <c:rotX val="15"/>
+      <c:rotY val="20"/>
+      <c:rAngAx val="0"/>
+    </c:view3D>
+    <c:floor>
+      <c:thickness val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+        <a:sp3d/>
+      </c:spPr>
+    </c:floor>
+    <c:sideWall>
+      <c:thickness val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+        <a:sp3d/>
+      </c:spPr>
+    </c:sideWall>
+    <c:backWall>
+      <c:thickness val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+        <a:sp3d/>
+      </c:spPr>
+    </c:backWall>
+    <c:plotArea>
+      <c:layout/>
+      <c:surface3DChart>
+        <c:wireframe val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$C$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln/>
+            <a:effectLst/>
+            <a:sp3d/>
+          </c:spPr>
+          <c:cat>
+            <c:numRef>
+              <c:f>Sheet1!$D$3:$N$3</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.4</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.6</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.7</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.8</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.9</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$D$4:$N$4</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>-</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>-</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>-</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>-</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>-</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>-</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>-</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-C11C-481F-BE05-5429115A7030}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$C$5</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>0.1</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln/>
+            <a:effectLst/>
+            <a:sp3d/>
+          </c:spPr>
+          <c:cat>
+            <c:numRef>
+              <c:f>Sheet1!$D$3:$N$3</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.4</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.6</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.7</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.8</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.9</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$D$5:$N$5</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>-</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.249668081622464E-5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2.855802549583541E-5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4.996253537858119E-5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>7.9907335070894417E-5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1.2477395663576204E-4</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1.9940232282984323E-4</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>3.4800306262219009E-4</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>7.867360294699096E-4</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>9.0042662426179938E-3</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>9.9999999999999992E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-C11C-481F-BE05-5429115A7030}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$C$6</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>0.2</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent3"/>
+            </a:solidFill>
+            <a:ln/>
+            <a:effectLst/>
+            <a:sp3d/>
+          </c:spPr>
+          <c:cat>
+            <c:numRef>
+              <c:f>Sheet1!$D$3:$N$3</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.4</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.6</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.7</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.8</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.9</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$D$6:$N$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>-</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2.855802549583541E-5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>6.6614868249287269E-5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.1985144854076157E-4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.9960109646253196E-4</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>3.3219075375397417E-4</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>5.9584325619141225E-4</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1.3689576703845251E-3</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1.2164832535435091E-2</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.1007867360294699</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.19999999999999987</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-C11C-481F-BE05-5429115A7030}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$C$7</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>0.3</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent4"/>
+            </a:solidFill>
+            <a:ln/>
+            <a:effectLst/>
+            <a:sp3d/>
+          </c:spPr>
+          <c:cat>
+            <c:numRef>
+              <c:f>Sheet1!$D$3:$N$3</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.4</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.6</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.7</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.8</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.9</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$D$7:$N$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>-</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4.996253537858119E-5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.1985144854076157E-4</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2.2453727765333505E-4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>3.9854114993964298E-4</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>7.4425615880137548E-4</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1.7535015565786393E-3</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1.400676357516902E-2</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.10136895767038451</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.20034800306262207</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.3</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-C11C-481F-BE05-5429115A7030}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="4"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$C$8</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>0.4</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent5"/>
+            </a:solidFill>
+            <a:ln/>
+            <a:effectLst/>
+            <a:sp3d/>
+          </c:spPr>
+          <c:cat>
+            <c:numRef>
+              <c:f>Sheet1!$D$3:$N$3</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.4</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.6</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.7</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.8</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.9</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$D$8:$N$8</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>-</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>7.9907335070894417E-5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.9960109646253196E-4</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3.9854114993964298E-4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>7.9367880419232983E-4</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1.9447161641415842E-3</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1.5007263393473431E-2</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.10175350155657864</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.20059584325619148</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.30019940232282982</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.39999999999999986</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000004-C11C-481F-BE05-5429115A7030}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="5"/>
+          <c:order val="5"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$C$9</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>0.5</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent6"/>
+            </a:solidFill>
+            <a:ln/>
+            <a:effectLst/>
+            <a:sp3d/>
+          </c:spPr>
+          <c:cat>
+            <c:numRef>
+              <c:f>Sheet1!$D$3:$N$3</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.4</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.6</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.7</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.8</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.9</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$D$9:$N$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>-</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.2477395663576204E-4</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3.3219075375397417E-4</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>7.4425615880137548E-4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.9447161641415842E-3</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1.5326715015857754E-2</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.10194471616414158</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.20074425615880123</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.30033219075375395</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.40012477395663559</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.49999999999999994</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000005-C11C-481F-BE05-5429115A7030}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="6"/>
+          <c:order val="6"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$C$10</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>0.6</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1">
+                <a:lumMod val="60000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln/>
+            <a:effectLst/>
+            <a:sp3d/>
+          </c:spPr>
+          <c:cat>
+            <c:numRef>
+              <c:f>Sheet1!$D$3:$N$3</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.4</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.6</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.7</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.8</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.9</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$D$10:$N$10</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>-</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.9940232282984323E-4</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>5.9584325619141225E-4</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.7535015565786393E-3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.5007263393473431E-2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.10194471616414158</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.20079367880419219</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.30039854114993936</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.40019960109646235</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.50007990733507079</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.60000000000000009</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000006-C11C-481F-BE05-5429115A7030}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="7"/>
+          <c:order val="7"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$C$11</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>0.7</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2">
+                <a:lumMod val="60000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln/>
+            <a:effectLst/>
+            <a:sp3d/>
+          </c:spPr>
+          <c:cat>
+            <c:numRef>
+              <c:f>Sheet1!$D$3:$N$3</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.4</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.6</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.7</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.8</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.9</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$D$11:$N$11</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>-</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3.4800306262219009E-4</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.3689576703845251E-3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.400676357516902E-2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.10175350155657864</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.20074425615880123</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.30039854114993936</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.40022453727765323</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.50011985144854065</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.60004996253537857</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.7</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000007-C11C-481F-BE05-5429115A7030}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="8"/>
+          <c:order val="8"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$C$12</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>0.8</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent3">
+                <a:lumMod val="60000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln/>
+            <a:effectLst/>
+            <a:sp3d/>
+          </c:spPr>
+          <c:cat>
+            <c:numRef>
+              <c:f>Sheet1!$D$3:$N$3</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.4</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.6</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.7</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.8</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.9</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$D$12:$N$12</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>-</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>7.867360294699096E-4</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.2164832535435091E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.10136895767038451</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.20059584325619148</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.30033219075375395</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.40019960109646235</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.50011985144854065</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.6000666148682493</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.70002855802549602</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.8</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000008-C11C-481F-BE05-5429115A7030}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="9"/>
+          <c:order val="9"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$C$13</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>0.9</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent4">
+                <a:lumMod val="60000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln/>
+            <a:effectLst/>
+            <a:sp3d/>
+          </c:spPr>
+          <c:cat>
+            <c:numRef>
+              <c:f>Sheet1!$D$3:$N$3</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.4</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.6</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.7</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.8</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.9</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$D$13:$N$13</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>-</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>9.0042662426179938E-3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.1007867360294699</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.20034800306262207</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.30019940232282982</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.40012477395663559</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.50007990733507079</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.60004996253537857</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.70002855802549602</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.8000124966808162</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.89999999999999991</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000009-C11C-481F-BE05-5429115A7030}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="10"/>
+          <c:order val="10"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$C$14</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent5">
+                <a:lumMod val="60000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln/>
+            <a:effectLst/>
+            <a:sp3d/>
+          </c:spPr>
+          <c:cat>
+            <c:numRef>
+              <c:f>Sheet1!$D$3:$N$3</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.4</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.6</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.7</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.8</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.9</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$D$14:$N$14</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>-</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>9.9999999999999992E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.19999999999999987</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.39999999999999986</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.49999999999999994</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.60000000000000009</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.7</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.8</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.89999999999999991</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{0000000A-C11C-481F-BE05-5429115A7030}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:bandFmts>
+          <c:bandFmt>
+            <c:idx val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln/>
+              <a:effectLst/>
+              <a:sp3d/>
+            </c:spPr>
+          </c:bandFmt>
+          <c:bandFmt>
+            <c:idx val="1"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln/>
+              <a:effectLst/>
+              <a:sp3d/>
+            </c:spPr>
+          </c:bandFmt>
+          <c:bandFmt>
+            <c:idx val="2"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln/>
+              <a:effectLst/>
+              <a:sp3d/>
+            </c:spPr>
+          </c:bandFmt>
+          <c:bandFmt>
+            <c:idx val="3"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:ln/>
+              <a:effectLst/>
+              <a:sp3d/>
+            </c:spPr>
+          </c:bandFmt>
+          <c:bandFmt>
+            <c:idx val="4"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent5"/>
+              </a:solidFill>
+              <a:ln/>
+              <a:effectLst/>
+              <a:sp3d/>
+            </c:spPr>
+          </c:bandFmt>
+          <c:bandFmt>
+            <c:idx val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent6"/>
+              </a:solidFill>
+              <a:ln/>
+              <a:effectLst/>
+              <a:sp3d/>
+            </c:spPr>
+          </c:bandFmt>
+          <c:bandFmt>
+            <c:idx val="6"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln/>
+              <a:effectLst/>
+              <a:sp3d/>
+            </c:spPr>
+          </c:bandFmt>
+          <c:bandFmt>
+            <c:idx val="7"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln/>
+              <a:effectLst/>
+              <a:sp3d/>
+            </c:spPr>
+          </c:bandFmt>
+          <c:bandFmt>
+            <c:idx val="8"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln/>
+              <a:effectLst/>
+              <a:sp3d/>
+            </c:spPr>
+          </c:bandFmt>
+          <c:bandFmt>
+            <c:idx val="9"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln/>
+              <a:effectLst/>
+              <a:sp3d/>
+            </c:spPr>
+          </c:bandFmt>
+          <c:bandFmt>
+            <c:idx val="10"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent5">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln/>
+              <a:effectLst/>
+              <a:sp3d/>
+            </c:spPr>
+          </c:bandFmt>
+          <c:bandFmt>
+            <c:idx val="11"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent6">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln/>
+              <a:effectLst/>
+              <a:sp3d/>
+            </c:spPr>
+          </c:bandFmt>
+          <c:bandFmt>
+            <c:idx val="12"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="80000"/>
+                  <a:lumOff val="20000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln/>
+              <a:effectLst/>
+              <a:sp3d/>
+            </c:spPr>
+          </c:bandFmt>
+          <c:bandFmt>
+            <c:idx val="13"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2">
+                  <a:lumMod val="80000"/>
+                  <a:lumOff val="20000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln/>
+              <a:effectLst/>
+              <a:sp3d/>
+            </c:spPr>
+          </c:bandFmt>
+          <c:bandFmt>
+            <c:idx val="14"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3">
+                  <a:lumMod val="80000"/>
+                  <a:lumOff val="20000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln/>
+              <a:effectLst/>
+              <a:sp3d/>
+            </c:spPr>
+          </c:bandFmt>
+        </c:bandFmts>
+        <c:axId val="821799935"/>
+        <c:axId val="821807135"/>
+        <c:axId val="592687663"/>
+      </c:surface3DChart>
+      <c:catAx>
+        <c:axId val="821799935"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="821807135"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="821807135"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="821799935"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:serAx>
+        <c:axId val="592687663"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="821807135"/>
+        <c:crosses val="autoZero"/>
+      </c:serAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr rtl="0">
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="zero"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>469106</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>100012</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>240506</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>100012</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="6" name="Chart 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DA6CBDEA-D6FA-7518-F949-C340D37B161C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="7" name="Chart 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DFA01640-CFC4-228E-F8E3-B788C92AA28B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -419,16 +4114,25 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E69DB58D-170D-4409-80B1-36FF0C79D9D9}">
-  <dimension ref="B3:N14"/>
+  <dimension ref="B2:P27"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
+  <cols>
+    <col min="1" max="1" width="3.578125" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="3" spans="2:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="B3" s="1" t="s">
+    <row r="2" spans="2:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
+      <c r="C2">
+        <v>1E-3</v>
+      </c>
+      <c r="P2">
+        <f>F9</f>
+        <v>3.3219075375397417E-4</v>
+      </c>
+    </row>
+    <row r="3" spans="2:16" x14ac:dyDescent="0.55000000000000004">
       <c r="D3">
         <v>0</v>
       </c>
@@ -463,62 +4167,1125 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="2:16" x14ac:dyDescent="0.55000000000000004">
       <c r="C4">
         <v>0</v>
       </c>
+      <c r="D4" cm="1">
+        <f t="array" ref="D4">_xll.PLACKETT($C4,D$3,theta)</f>
+        <v>0</v>
+      </c>
+      <c r="E4" cm="1">
+        <f t="array" ref="E4">_xll.PLACKETT($C4,E$3,theta)</f>
+        <v>0</v>
+      </c>
+      <c r="F4" cm="1">
+        <f t="array" ref="F4">_xll.PLACKETT($C4,F$3,theta)</f>
+        <v>0</v>
+      </c>
+      <c r="G4" cm="1">
+        <f t="array" ref="G4">_xll.PLACKETT($C4,G$3,theta)</f>
+        <v>0</v>
+      </c>
+      <c r="H4" cm="1">
+        <f t="array" ref="H4">_xll.PLACKETT($C4,H$3,theta)</f>
+        <v>0</v>
+      </c>
+      <c r="I4" cm="1">
+        <f t="array" ref="I4">_xll.PLACKETT($C4,I$3,theta)</f>
+        <v>0</v>
+      </c>
+      <c r="J4" cm="1">
+        <f t="array" ref="J4">_xll.PLACKETT($C4,J$3,theta)</f>
+        <v>0</v>
+      </c>
+      <c r="K4" cm="1">
+        <f t="array" ref="K4">_xll.PLACKETT($C4,K$3,theta)</f>
+        <v>0</v>
+      </c>
+      <c r="L4" cm="1">
+        <f t="array" ref="L4">_xll.PLACKETT($C4,L$3,theta)</f>
+        <v>0</v>
+      </c>
+      <c r="M4" cm="1">
+        <f t="array" ref="M4">_xll.PLACKETT($C4,M$3,theta)</f>
+        <v>0</v>
+      </c>
+      <c r="N4" cm="1">
+        <f t="array" ref="N4">_xll.PLACKETT($C4,N$3,theta)</f>
+        <v>0</v>
+      </c>
     </row>
-    <row r="5" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="2:16" x14ac:dyDescent="0.55000000000000004">
       <c r="C5">
         <v>0.1</v>
       </c>
+      <c r="D5" cm="1">
+        <f t="array" ref="D5">_xll.PLACKETT($C5,D$3,theta)</f>
+        <v>0</v>
+      </c>
+      <c r="E5" cm="1">
+        <f t="array" ref="E5">_xll.PLACKETT($C5,E$3,theta)</f>
+        <v>1.249668081622464E-5</v>
+      </c>
+      <c r="F5" cm="1">
+        <f t="array" ref="F5">_xll.PLACKETT($C5,F$3,theta)</f>
+        <v>2.855802549583541E-5</v>
+      </c>
+      <c r="G5" cm="1">
+        <f t="array" ref="G5">_xll.PLACKETT($C5,G$3,theta)</f>
+        <v>4.996253537858119E-5</v>
+      </c>
+      <c r="H5" cm="1">
+        <f t="array" ref="H5">_xll.PLACKETT($C5,H$3,theta)</f>
+        <v>7.9907335070894417E-5</v>
+      </c>
+      <c r="I5" cm="1">
+        <f t="array" ref="I5">_xll.PLACKETT($C5,I$3,theta)</f>
+        <v>1.2477395663576204E-4</v>
+      </c>
+      <c r="J5" cm="1">
+        <f t="array" ref="J5">_xll.PLACKETT($C5,J$3,theta)</f>
+        <v>1.9940232282984323E-4</v>
+      </c>
+      <c r="K5" cm="1">
+        <f t="array" ref="K5">_xll.PLACKETT($C5,K$3,theta)</f>
+        <v>3.4800306262219009E-4</v>
+      </c>
+      <c r="L5" cm="1">
+        <f t="array" ref="L5">_xll.PLACKETT($C5,L$3,theta)</f>
+        <v>7.867360294699096E-4</v>
+      </c>
+      <c r="M5" cm="1">
+        <f t="array" ref="M5">_xll.PLACKETT($C5,M$3,theta)</f>
+        <v>9.0042662426179938E-3</v>
+      </c>
+      <c r="N5" cm="1">
+        <f t="array" ref="N5">_xll.PLACKETT($C5,N$3,theta)</f>
+        <v>9.9999999999999992E-2</v>
+      </c>
     </row>
-    <row r="6" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="2:16" x14ac:dyDescent="0.55000000000000004">
       <c r="C6">
         <v>0.2</v>
       </c>
+      <c r="D6" cm="1">
+        <f t="array" ref="D6">_xll.PLACKETT($C6,D$3,theta)</f>
+        <v>0</v>
+      </c>
+      <c r="E6" cm="1">
+        <f t="array" ref="E6">_xll.PLACKETT($C6,E$3,theta)</f>
+        <v>2.855802549583541E-5</v>
+      </c>
+      <c r="F6" cm="1">
+        <f t="array" ref="F6">_xll.PLACKETT($C6,F$3,theta)</f>
+        <v>6.6614868249287269E-5</v>
+      </c>
+      <c r="G6" cm="1">
+        <f t="array" ref="G6">_xll.PLACKETT($C6,G$3,theta)</f>
+        <v>1.1985144854076157E-4</v>
+      </c>
+      <c r="H6" cm="1">
+        <f t="array" ref="H6">_xll.PLACKETT($C6,H$3,theta)</f>
+        <v>1.9960109646253196E-4</v>
+      </c>
+      <c r="I6" cm="1">
+        <f t="array" ref="I6">_xll.PLACKETT($C6,I$3,theta)</f>
+        <v>3.3219075375397417E-4</v>
+      </c>
+      <c r="J6" cm="1">
+        <f t="array" ref="J6">_xll.PLACKETT($C6,J$3,theta)</f>
+        <v>5.9584325619141225E-4</v>
+      </c>
+      <c r="K6" cm="1">
+        <f t="array" ref="K6">_xll.PLACKETT($C6,K$3,theta)</f>
+        <v>1.3689576703845251E-3</v>
+      </c>
+      <c r="L6" cm="1">
+        <f t="array" ref="L6">_xll.PLACKETT($C6,L$3,theta)</f>
+        <v>1.2164832535435091E-2</v>
+      </c>
+      <c r="M6" cm="1">
+        <f t="array" ref="M6">_xll.PLACKETT($C6,M$3,theta)</f>
+        <v>0.1007867360294699</v>
+      </c>
+      <c r="N6" cm="1">
+        <f t="array" ref="N6">_xll.PLACKETT($C6,N$3,theta)</f>
+        <v>0.19999999999999987</v>
+      </c>
     </row>
-    <row r="7" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="2:16" x14ac:dyDescent="0.55000000000000004">
       <c r="C7">
         <v>0.3</v>
       </c>
+      <c r="D7" cm="1">
+        <f t="array" ref="D7">_xll.PLACKETT($C7,D$3,theta)</f>
+        <v>0</v>
+      </c>
+      <c r="E7" cm="1">
+        <f t="array" ref="E7">_xll.PLACKETT($C7,E$3,theta)</f>
+        <v>4.996253537858119E-5</v>
+      </c>
+      <c r="F7" cm="1">
+        <f t="array" ref="F7">_xll.PLACKETT($C7,F$3,theta)</f>
+        <v>1.1985144854076157E-4</v>
+      </c>
+      <c r="G7" cm="1">
+        <f t="array" ref="G7">_xll.PLACKETT($C7,G$3,theta)</f>
+        <v>2.2453727765333505E-4</v>
+      </c>
+      <c r="H7" cm="1">
+        <f t="array" ref="H7">_xll.PLACKETT($C7,H$3,theta)</f>
+        <v>3.9854114993964298E-4</v>
+      </c>
+      <c r="I7" cm="1">
+        <f t="array" ref="I7">_xll.PLACKETT($C7,I$3,theta)</f>
+        <v>7.4425615880137548E-4</v>
+      </c>
+      <c r="J7" cm="1">
+        <f t="array" ref="J7">_xll.PLACKETT($C7,J$3,theta)</f>
+        <v>1.7535015565786393E-3</v>
+      </c>
+      <c r="K7" cm="1">
+        <f t="array" ref="K7">_xll.PLACKETT($C7,K$3,theta)</f>
+        <v>1.400676357516902E-2</v>
+      </c>
+      <c r="L7" cm="1">
+        <f t="array" ref="L7">_xll.PLACKETT($C7,L$3,theta)</f>
+        <v>0.10136895767038451</v>
+      </c>
+      <c r="M7" cm="1">
+        <f t="array" ref="M7">_xll.PLACKETT($C7,M$3,theta)</f>
+        <v>0.20034800306262207</v>
+      </c>
+      <c r="N7" cm="1">
+        <f t="array" ref="N7">_xll.PLACKETT($C7,N$3,theta)</f>
+        <v>0.3</v>
+      </c>
     </row>
-    <row r="8" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="2:16" x14ac:dyDescent="0.55000000000000004">
       <c r="C8">
         <v>0.4</v>
       </c>
+      <c r="D8" cm="1">
+        <f t="array" ref="D8">_xll.PLACKETT($C8,D$3,theta)</f>
+        <v>0</v>
+      </c>
+      <c r="E8" cm="1">
+        <f t="array" ref="E8">_xll.PLACKETT($C8,E$3,theta)</f>
+        <v>7.9907335070894417E-5</v>
+      </c>
+      <c r="F8" cm="1">
+        <f t="array" ref="F8">_xll.PLACKETT($C8,F$3,theta)</f>
+        <v>1.9960109646253196E-4</v>
+      </c>
+      <c r="G8" cm="1">
+        <f t="array" ref="G8">_xll.PLACKETT($C8,G$3,theta)</f>
+        <v>3.9854114993964298E-4</v>
+      </c>
+      <c r="H8" cm="1">
+        <f t="array" ref="H8">_xll.PLACKETT($C8,H$3,theta)</f>
+        <v>7.9367880419232983E-4</v>
+      </c>
+      <c r="I8" cm="1">
+        <f t="array" ref="I8">_xll.PLACKETT($C8,I$3,theta)</f>
+        <v>1.9447161641415842E-3</v>
+      </c>
+      <c r="J8" cm="1">
+        <f t="array" ref="J8">_xll.PLACKETT($C8,J$3,theta)</f>
+        <v>1.5007263393473431E-2</v>
+      </c>
+      <c r="K8" cm="1">
+        <f t="array" ref="K8">_xll.PLACKETT($C8,K$3,theta)</f>
+        <v>0.10175350155657864</v>
+      </c>
+      <c r="L8" cm="1">
+        <f t="array" ref="L8">_xll.PLACKETT($C8,L$3,theta)</f>
+        <v>0.20059584325619148</v>
+      </c>
+      <c r="M8" cm="1">
+        <f t="array" ref="M8">_xll.PLACKETT($C8,M$3,theta)</f>
+        <v>0.30019940232282982</v>
+      </c>
+      <c r="N8" cm="1">
+        <f t="array" ref="N8">_xll.PLACKETT($C8,N$3,theta)</f>
+        <v>0.39999999999999986</v>
+      </c>
     </row>
-    <row r="9" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="2:16" x14ac:dyDescent="0.55000000000000004">
       <c r="C9">
         <v>0.5</v>
       </c>
+      <c r="D9" cm="1">
+        <f t="array" ref="D9">_xll.PLACKETT($C9,D$3,theta)</f>
+        <v>0</v>
+      </c>
+      <c r="E9" cm="1">
+        <f t="array" ref="E9">_xll.PLACKETT($C9,E$3,theta)</f>
+        <v>1.2477395663576204E-4</v>
+      </c>
+      <c r="F9" cm="1">
+        <f t="array" ref="F9">_xll.PLACKETT($C9,F$3,theta)</f>
+        <v>3.3219075375397417E-4</v>
+      </c>
+      <c r="G9" cm="1">
+        <f t="array" ref="G9">_xll.PLACKETT($C9,G$3,theta)</f>
+        <v>7.4425615880137548E-4</v>
+      </c>
+      <c r="H9" cm="1">
+        <f t="array" ref="H9">_xll.PLACKETT($C9,H$3,theta)</f>
+        <v>1.9447161641415842E-3</v>
+      </c>
+      <c r="I9" cm="1">
+        <f t="array" ref="I9">_xll.PLACKETT($C9,I$3,theta)</f>
+        <v>1.5326715015857754E-2</v>
+      </c>
+      <c r="J9" cm="1">
+        <f t="array" ref="J9">_xll.PLACKETT($C9,J$3,theta)</f>
+        <v>0.10194471616414158</v>
+      </c>
+      <c r="K9" cm="1">
+        <f t="array" ref="K9">_xll.PLACKETT($C9,K$3,theta)</f>
+        <v>0.20074425615880123</v>
+      </c>
+      <c r="L9" cm="1">
+        <f t="array" ref="L9">_xll.PLACKETT($C9,L$3,theta)</f>
+        <v>0.30033219075375395</v>
+      </c>
+      <c r="M9" cm="1">
+        <f t="array" ref="M9">_xll.PLACKETT($C9,M$3,theta)</f>
+        <v>0.40012477395663559</v>
+      </c>
+      <c r="N9" cm="1">
+        <f t="array" ref="N9">_xll.PLACKETT($C9,N$3,theta)</f>
+        <v>0.49999999999999994</v>
+      </c>
     </row>
-    <row r="10" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="2:16" x14ac:dyDescent="0.55000000000000004">
       <c r="C10">
         <v>0.6</v>
       </c>
+      <c r="D10" cm="1">
+        <f t="array" ref="D10">_xll.PLACKETT($C10,D$3,theta)</f>
+        <v>0</v>
+      </c>
+      <c r="E10" cm="1">
+        <f t="array" ref="E10">_xll.PLACKETT($C10,E$3,theta)</f>
+        <v>1.9940232282984323E-4</v>
+      </c>
+      <c r="F10" cm="1">
+        <f t="array" ref="F10">_xll.PLACKETT($C10,F$3,theta)</f>
+        <v>5.9584325619141225E-4</v>
+      </c>
+      <c r="G10" cm="1">
+        <f t="array" ref="G10">_xll.PLACKETT($C10,G$3,theta)</f>
+        <v>1.7535015565786393E-3</v>
+      </c>
+      <c r="H10" cm="1">
+        <f t="array" ref="H10">_xll.PLACKETT($C10,H$3,theta)</f>
+        <v>1.5007263393473431E-2</v>
+      </c>
+      <c r="I10" cm="1">
+        <f t="array" ref="I10">_xll.PLACKETT($C10,I$3,theta)</f>
+        <v>0.10194471616414158</v>
+      </c>
+      <c r="J10" cm="1">
+        <f t="array" ref="J10">_xll.PLACKETT($C10,J$3,theta)</f>
+        <v>0.20079367880419219</v>
+      </c>
+      <c r="K10" cm="1">
+        <f t="array" ref="K10">_xll.PLACKETT($C10,K$3,theta)</f>
+        <v>0.30039854114993936</v>
+      </c>
+      <c r="L10" cm="1">
+        <f t="array" ref="L10">_xll.PLACKETT($C10,L$3,theta)</f>
+        <v>0.40019960109646235</v>
+      </c>
+      <c r="M10" cm="1">
+        <f t="array" ref="M10">_xll.PLACKETT($C10,M$3,theta)</f>
+        <v>0.50007990733507079</v>
+      </c>
+      <c r="N10" cm="1">
+        <f t="array" ref="N10">_xll.PLACKETT($C10,N$3,theta)</f>
+        <v>0.60000000000000009</v>
+      </c>
     </row>
-    <row r="11" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="2:16" x14ac:dyDescent="0.55000000000000004">
       <c r="C11">
         <v>0.7</v>
       </c>
+      <c r="D11" cm="1">
+        <f t="array" ref="D11">_xll.PLACKETT($C11,D$3,theta)</f>
+        <v>0</v>
+      </c>
+      <c r="E11" cm="1">
+        <f t="array" ref="E11">_xll.PLACKETT($C11,E$3,theta)</f>
+        <v>3.4800306262219009E-4</v>
+      </c>
+      <c r="F11" cm="1">
+        <f t="array" ref="F11">_xll.PLACKETT($C11,F$3,theta)</f>
+        <v>1.3689576703845251E-3</v>
+      </c>
+      <c r="G11" cm="1">
+        <f t="array" ref="G11">_xll.PLACKETT($C11,G$3,theta)</f>
+        <v>1.400676357516902E-2</v>
+      </c>
+      <c r="H11" cm="1">
+        <f t="array" ref="H11">_xll.PLACKETT($C11,H$3,theta)</f>
+        <v>0.10175350155657864</v>
+      </c>
+      <c r="I11" cm="1">
+        <f t="array" ref="I11">_xll.PLACKETT($C11,I$3,theta)</f>
+        <v>0.20074425615880123</v>
+      </c>
+      <c r="J11" cm="1">
+        <f t="array" ref="J11">_xll.PLACKETT($C11,J$3,theta)</f>
+        <v>0.30039854114993936</v>
+      </c>
+      <c r="K11" cm="1">
+        <f t="array" ref="K11">_xll.PLACKETT($C11,K$3,theta)</f>
+        <v>0.40022453727765323</v>
+      </c>
+      <c r="L11" cm="1">
+        <f t="array" ref="L11">_xll.PLACKETT($C11,L$3,theta)</f>
+        <v>0.50011985144854065</v>
+      </c>
+      <c r="M11" cm="1">
+        <f t="array" ref="M11">_xll.PLACKETT($C11,M$3,theta)</f>
+        <v>0.60004996253537857</v>
+      </c>
+      <c r="N11" cm="1">
+        <f t="array" ref="N11">_xll.PLACKETT($C11,N$3,theta)</f>
+        <v>0.7</v>
+      </c>
     </row>
-    <row r="12" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="2:16" x14ac:dyDescent="0.55000000000000004">
       <c r="C12">
         <v>0.8</v>
       </c>
+      <c r="D12" cm="1">
+        <f t="array" ref="D12">_xll.PLACKETT($C12,D$3,theta)</f>
+        <v>0</v>
+      </c>
+      <c r="E12" cm="1">
+        <f t="array" ref="E12">_xll.PLACKETT($C12,E$3,theta)</f>
+        <v>7.867360294699096E-4</v>
+      </c>
+      <c r="F12" cm="1">
+        <f t="array" ref="F12">_xll.PLACKETT($C12,F$3,theta)</f>
+        <v>1.2164832535435091E-2</v>
+      </c>
+      <c r="G12" cm="1">
+        <f t="array" ref="G12">_xll.PLACKETT($C12,G$3,theta)</f>
+        <v>0.10136895767038451</v>
+      </c>
+      <c r="H12" cm="1">
+        <f t="array" ref="H12">_xll.PLACKETT($C12,H$3,theta)</f>
+        <v>0.20059584325619148</v>
+      </c>
+      <c r="I12" cm="1">
+        <f t="array" ref="I12">_xll.PLACKETT($C12,I$3,theta)</f>
+        <v>0.30033219075375395</v>
+      </c>
+      <c r="J12" cm="1">
+        <f t="array" ref="J12">_xll.PLACKETT($C12,J$3,theta)</f>
+        <v>0.40019960109646235</v>
+      </c>
+      <c r="K12" cm="1">
+        <f t="array" ref="K12">_xll.PLACKETT($C12,K$3,theta)</f>
+        <v>0.50011985144854065</v>
+      </c>
+      <c r="L12" cm="1">
+        <f t="array" ref="L12">_xll.PLACKETT($C12,L$3,theta)</f>
+        <v>0.6000666148682493</v>
+      </c>
+      <c r="M12" cm="1">
+        <f t="array" ref="M12">_xll.PLACKETT($C12,M$3,theta)</f>
+        <v>0.70002855802549602</v>
+      </c>
+      <c r="N12" cm="1">
+        <f t="array" ref="N12">_xll.PLACKETT($C12,N$3,theta)</f>
+        <v>0.8</v>
+      </c>
     </row>
-    <row r="13" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="2:16" x14ac:dyDescent="0.55000000000000004">
       <c r="C13">
         <v>0.9</v>
       </c>
+      <c r="D13" cm="1">
+        <f t="array" ref="D13">_xll.PLACKETT($C13,D$3,theta)</f>
+        <v>0</v>
+      </c>
+      <c r="E13" cm="1">
+        <f t="array" ref="E13">_xll.PLACKETT($C13,E$3,theta)</f>
+        <v>9.0042662426179938E-3</v>
+      </c>
+      <c r="F13" cm="1">
+        <f t="array" ref="F13">_xll.PLACKETT($C13,F$3,theta)</f>
+        <v>0.1007867360294699</v>
+      </c>
+      <c r="G13" cm="1">
+        <f t="array" ref="G13">_xll.PLACKETT($C13,G$3,theta)</f>
+        <v>0.20034800306262207</v>
+      </c>
+      <c r="H13" cm="1">
+        <f t="array" ref="H13">_xll.PLACKETT($C13,H$3,theta)</f>
+        <v>0.30019940232282982</v>
+      </c>
+      <c r="I13" cm="1">
+        <f t="array" ref="I13">_xll.PLACKETT($C13,I$3,theta)</f>
+        <v>0.40012477395663559</v>
+      </c>
+      <c r="J13" cm="1">
+        <f t="array" ref="J13">_xll.PLACKETT($C13,J$3,theta)</f>
+        <v>0.50007990733507079</v>
+      </c>
+      <c r="K13" cm="1">
+        <f t="array" ref="K13">_xll.PLACKETT($C13,K$3,theta)</f>
+        <v>0.60004996253537857</v>
+      </c>
+      <c r="L13" cm="1">
+        <f t="array" ref="L13">_xll.PLACKETT($C13,L$3,theta)</f>
+        <v>0.70002855802549602</v>
+      </c>
+      <c r="M13" cm="1">
+        <f t="array" ref="M13">_xll.PLACKETT($C13,M$3,theta)</f>
+        <v>0.8000124966808162</v>
+      </c>
+      <c r="N13" cm="1">
+        <f t="array" ref="N13">_xll.PLACKETT($C13,N$3,theta)</f>
+        <v>0.89999999999999991</v>
+      </c>
     </row>
-    <row r="14" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="2:16" x14ac:dyDescent="0.55000000000000004">
       <c r="C14">
         <v>1</v>
+      </c>
+      <c r="D14" cm="1">
+        <f t="array" ref="D14">_xll.PLACKETT($C14,D$3,theta)</f>
+        <v>0</v>
+      </c>
+      <c r="E14" cm="1">
+        <f t="array" ref="E14">_xll.PLACKETT($C14,E$3,theta)</f>
+        <v>9.9999999999999992E-2</v>
+      </c>
+      <c r="F14" cm="1">
+        <f t="array" ref="F14">_xll.PLACKETT($C14,F$3,theta)</f>
+        <v>0.19999999999999987</v>
+      </c>
+      <c r="G14" cm="1">
+        <f t="array" ref="G14">_xll.PLACKETT($C14,G$3,theta)</f>
+        <v>0.3</v>
+      </c>
+      <c r="H14" cm="1">
+        <f t="array" ref="H14">_xll.PLACKETT($C14,H$3,theta)</f>
+        <v>0.39999999999999986</v>
+      </c>
+      <c r="I14" cm="1">
+        <f t="array" ref="I14">_xll.PLACKETT($C14,I$3,theta)</f>
+        <v>0.49999999999999994</v>
+      </c>
+      <c r="J14" cm="1">
+        <f t="array" ref="J14">_xll.PLACKETT($C14,J$3,theta)</f>
+        <v>0.60000000000000009</v>
+      </c>
+      <c r="K14" cm="1">
+        <f t="array" ref="K14">_xll.PLACKETT($C14,K$3,theta)</f>
+        <v>0.7</v>
+      </c>
+      <c r="L14" cm="1">
+        <f t="array" ref="L14">_xll.PLACKETT($C14,L$3,theta)</f>
+        <v>0.8</v>
+      </c>
+      <c r="M14" cm="1">
+        <f t="array" ref="M14">_xll.PLACKETT($C14,M$3,theta)</f>
+        <v>0.89999999999999991</v>
+      </c>
+      <c r="N14" cm="1">
+        <f t="array" ref="N14">_xll.PLACKETT($C14,N$3,theta)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="2:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="D16">
+        <v>0</v>
+      </c>
+      <c r="E16">
+        <v>0.1</v>
+      </c>
+      <c r="F16">
+        <v>0.2</v>
+      </c>
+      <c r="G16">
+        <v>0.3</v>
+      </c>
+      <c r="H16">
+        <v>0.4</v>
+      </c>
+      <c r="I16">
+        <v>0.5</v>
+      </c>
+      <c r="J16">
+        <v>0.6</v>
+      </c>
+      <c r="K16">
+        <v>0.7</v>
+      </c>
+      <c r="L16">
+        <v>0.8</v>
+      </c>
+      <c r="M16">
+        <v>0.9</v>
+      </c>
+      <c r="N16">
+        <v>1</v>
+      </c>
+      <c r="P16">
+        <f>SUM(M17:M27)/11</f>
+        <v>2.4381778898280388</v>
+      </c>
+    </row>
+    <row r="17" spans="3:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="C17">
+        <v>0</v>
+      </c>
+      <c r="D17" cm="1">
+        <f t="array" ref="D17">_xll.PLACKETT.UV($C17,D$3,theta)</f>
+        <v>1E-3</v>
+      </c>
+      <c r="E17" cm="1">
+        <f t="array" ref="E17">_xll.PLACKETT.UV($C17,E$3,theta)</f>
+        <v>1.2342935985300352E-3</v>
+      </c>
+      <c r="F17" cm="1">
+        <f t="array" ref="F17">_xll.PLACKETT.UV($C17,F$3,theta)</f>
+        <v>1.5617190428711242E-3</v>
+      </c>
+      <c r="G17" cm="1">
+        <f t="array" ref="G17">_xll.PLACKETT.UV($C17,G$3,theta)</f>
+        <v>2.0390681792827859E-3</v>
+      </c>
+      <c r="H17" cm="1">
+        <f t="array" ref="H17">_xll.PLACKETT.UV($C17,H$3,theta)</f>
+        <v>2.7740777744883374E-3</v>
+      </c>
+      <c r="I17" cm="1">
+        <f t="array" ref="I17">_xll.PLACKETT.UV($C17,I$3,theta)</f>
+        <v>3.9920119840199777E-3</v>
+      </c>
+      <c r="J17" cm="1">
+        <f t="array" ref="J17">_xll.PLACKETT.UV($C17,J$3,theta)</f>
+        <v>6.2312921032829172E-3</v>
+      </c>
+      <c r="K17" cm="1">
+        <f t="array" ref="K17">_xll.PLACKETT.UV($C17,K$3,theta)</f>
+        <v>1.105944017777386E-2</v>
+      </c>
+      <c r="L17" cm="1">
+        <f t="array" ref="L17">_xll.PLACKETT.UV($C17,L$3,theta)</f>
+        <v>2.4801193631847115E-2</v>
+      </c>
+      <c r="M17" cm="1">
+        <f t="array" ref="M17">_xll.PLACKETT.UV($C17,M$3,theta)</f>
+        <v>9.8224011645438827E-2</v>
+      </c>
+      <c r="N17" cm="1">
+        <f t="array" ref="N17">_xll.PLACKETT.UV($C17,N$3,theta)</f>
+        <v>999.99999999999829</v>
+      </c>
+    </row>
+    <row r="18" spans="3:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="C18">
+        <v>0.1</v>
+      </c>
+      <c r="D18" cm="1">
+        <f t="array" ref="D18">_xll.PLACKETT.UV($C18,D$3,theta)</f>
+        <v>1.2342935985300352E-3</v>
+      </c>
+      <c r="E18" cm="1">
+        <f t="array" ref="E18">_xll.PLACKETT.UV($C18,E$3,theta)</f>
+        <v>1.6005633972407799E-3</v>
+      </c>
+      <c r="F18" cm="1">
+        <f t="array" ref="F18">_xll.PLACKETT.UV($C18,F$3,theta)</f>
+        <v>2.1548932066352512E-3</v>
+      </c>
+      <c r="G18" cm="1">
+        <f t="array" ref="G18">_xll.PLACKETT.UV($C18,G$3,theta)</f>
+        <v>3.0495021897984347E-3</v>
+      </c>
+      <c r="H18" cm="1">
+        <f t="array" ref="H18">_xll.PLACKETT.UV($C18,H$3,theta)</f>
+        <v>4.6250302965488033E-3</v>
+      </c>
+      <c r="I18" cm="1">
+        <f t="array" ref="I18">_xll.PLACKETT.UV($C18,I$3,theta)</f>
+        <v>7.7707099460882492E-3</v>
+      </c>
+      <c r="J18" cm="1">
+        <f t="array" ref="J18">_xll.PLACKETT.UV($C18,J$3,theta)</f>
+        <v>1.5407183256802326E-2</v>
+      </c>
+      <c r="K18" cm="1">
+        <f t="array" ref="K18">_xll.PLACKETT.UV($C18,K$3,theta)</f>
+        <v>4.1641495228951074E-2</v>
+      </c>
+      <c r="L18" cm="1">
+        <f t="array" ref="L18">_xll.PLACKETT.UV($C18,L$3,theta)</f>
+        <v>0.24232226107297336</v>
+      </c>
+      <c r="M18" cm="1">
+        <f t="array" ref="M18">_xll.PLACKETT.UV($C18,M$3,theta)</f>
+        <v>26.401926844269422</v>
+      </c>
+      <c r="N18" cm="1">
+        <f t="array" ref="N18">_xll.PLACKETT.UV($C18,N$3,theta)</f>
+        <v>9.8224011645438758E-2</v>
+      </c>
+    </row>
+    <row r="19" spans="3:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="C19">
+        <v>0.2</v>
+      </c>
+      <c r="D19" cm="1">
+        <f t="array" ref="D19">_xll.PLACKETT.UV($C19,D$3,theta)</f>
+        <v>1.5617190428711242E-3</v>
+      </c>
+      <c r="E19" cm="1">
+        <f t="array" ref="E19">_xll.PLACKETT.UV($C19,E$3,theta)</f>
+        <v>2.1548932066352512E-3</v>
+      </c>
+      <c r="F19" cm="1">
+        <f t="array" ref="F19">_xll.PLACKETT.UV($C19,F$3,theta)</f>
+        <v>3.141249243121604E-3</v>
+      </c>
+      <c r="G19" cm="1">
+        <f t="array" ref="G19">_xll.PLACKETT.UV($C19,G$3,theta)</f>
+        <v>4.9410850590055049E-3</v>
+      </c>
+      <c r="H19" cm="1">
+        <f t="array" ref="H19">_xll.PLACKETT.UV($C19,H$3,theta)</f>
+        <v>8.6916032918170089E-3</v>
+      </c>
+      <c r="I19" cm="1">
+        <f t="array" ref="I19">_xll.PLACKETT.UV($C19,I$3,theta)</f>
+        <v>1.828652524625822E-2</v>
+      </c>
+      <c r="J19" cm="1">
+        <f t="array" ref="J19">_xll.PLACKETT.UV($C19,J$3,theta)</f>
+        <v>5.3457945533076284E-2</v>
+      </c>
+      <c r="K19" cm="1">
+        <f t="array" ref="K19">_xll.PLACKETT.UV($C19,K$3,theta)</f>
+        <v>0.34195583529660456</v>
+      </c>
+      <c r="L19" cm="1">
+        <f t="array" ref="L19">_xll.PLACKETT.UV($C19,L$3,theta)</f>
+        <v>19.789534608545942</v>
+      </c>
+      <c r="M19" cm="1">
+        <f t="array" ref="M19">_xll.PLACKETT.UV($C19,M$3,theta)</f>
+        <v>0.24232226107297336</v>
+      </c>
+      <c r="N19" cm="1">
+        <f t="array" ref="N19">_xll.PLACKETT.UV($C19,N$3,theta)</f>
+        <v>2.4801193631847174E-2</v>
+      </c>
+    </row>
+    <row r="20" spans="3:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="C20">
+        <v>0.3</v>
+      </c>
+      <c r="D20" cm="1">
+        <f t="array" ref="D20">_xll.PLACKETT.UV($C20,D$3,theta)</f>
+        <v>2.0390681792827859E-3</v>
+      </c>
+      <c r="E20" cm="1">
+        <f t="array" ref="E20">_xll.PLACKETT.UV($C20,E$3,theta)</f>
+        <v>3.0495021897984347E-3</v>
+      </c>
+      <c r="F20" cm="1">
+        <f t="array" ref="F20">_xll.PLACKETT.UV($C20,F$3,theta)</f>
+        <v>4.9410850590055049E-3</v>
+      </c>
+      <c r="G20" cm="1">
+        <f t="array" ref="G20">_xll.PLACKETT.UV($C20,G$3,theta)</f>
+        <v>8.9981094652824591E-3</v>
+      </c>
+      <c r="H20" cm="1">
+        <f t="array" ref="H20">_xll.PLACKETT.UV($C20,H$3,theta)</f>
+        <v>1.9720488121697521E-2</v>
+      </c>
+      <c r="I20" cm="1">
+        <f t="array" ref="I20">_xll.PLACKETT.UV($C20,I$3,theta)</f>
+        <v>6.0464436173095923E-2</v>
+      </c>
+      <c r="J20" cm="1">
+        <f t="array" ref="J20">_xll.PLACKETT.UV($C20,J$3,theta)</f>
+        <v>0.40468977437845532</v>
+      </c>
+      <c r="K20" cm="1">
+        <f t="array" ref="K20">_xll.PLACKETT.UV($C20,K$3,theta)</f>
+        <v>17.270528003950261</v>
+      </c>
+      <c r="L20" cm="1">
+        <f t="array" ref="L20">_xll.PLACKETT.UV($C20,L$3,theta)</f>
+        <v>0.3419558352966055</v>
+      </c>
+      <c r="M20" cm="1">
+        <f t="array" ref="M20">_xll.PLACKETT.UV($C20,M$3,theta)</f>
+        <v>4.1641495228951206E-2</v>
+      </c>
+      <c r="N20" cm="1">
+        <f t="array" ref="N20">_xll.PLACKETT.UV($C20,N$3,theta)</f>
+        <v>1.1059440177773869E-2</v>
+      </c>
+    </row>
+    <row r="21" spans="3:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="C21">
+        <v>0.4</v>
+      </c>
+      <c r="D21" cm="1">
+        <f t="array" ref="D21">_xll.PLACKETT.UV($C21,D$3,theta)</f>
+        <v>2.7740777744883374E-3</v>
+      </c>
+      <c r="E21" cm="1">
+        <f t="array" ref="E21">_xll.PLACKETT.UV($C21,E$3,theta)</f>
+        <v>4.6250302965488033E-3</v>
+      </c>
+      <c r="F21" cm="1">
+        <f t="array" ref="F21">_xll.PLACKETT.UV($C21,F$3,theta)</f>
+        <v>8.6916032918170089E-3</v>
+      </c>
+      <c r="G21" cm="1">
+        <f t="array" ref="G21">_xll.PLACKETT.UV($C21,G$3,theta)</f>
+        <v>1.9720488121697521E-2</v>
+      </c>
+      <c r="H21" cm="1">
+        <f t="array" ref="H21">_xll.PLACKETT.UV($C21,H$3,theta)</f>
+        <v>6.2786189138963278E-2</v>
+      </c>
+      <c r="I21" cm="1">
+        <f t="array" ref="I21">_xll.PLACKETT.UV($C21,I$3,theta)</f>
+        <v>0.43501073894100922</v>
+      </c>
+      <c r="J21" cm="1">
+        <f t="array" ref="J21">_xll.PLACKETT.UV($C21,J$3,theta)</f>
+        <v>16.153903196224309</v>
+      </c>
+      <c r="K21" cm="1">
+        <f t="array" ref="K21">_xll.PLACKETT.UV($C21,K$3,theta)</f>
+        <v>0.40468977437845638</v>
+      </c>
+      <c r="L21" cm="1">
+        <f t="array" ref="L21">_xll.PLACKETT.UV($C21,L$3,theta)</f>
+        <v>5.3457945533076208E-2</v>
+      </c>
+      <c r="M21" cm="1">
+        <f t="array" ref="M21">_xll.PLACKETT.UV($C21,M$3,theta)</f>
+        <v>1.5407183256802345E-2</v>
+      </c>
+      <c r="N21" cm="1">
+        <f t="array" ref="N21">_xll.PLACKETT.UV($C21,N$3,theta)</f>
+        <v>6.2312921032829285E-3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="C22">
+        <v>0.5</v>
+      </c>
+      <c r="D22" cm="1">
+        <f t="array" ref="D22">_xll.PLACKETT.UV($C22,D$3,theta)</f>
+        <v>3.9920119840199777E-3</v>
+      </c>
+      <c r="E22" cm="1">
+        <f t="array" ref="E22">_xll.PLACKETT.UV($C22,E$3,theta)</f>
+        <v>7.7707099460882492E-3</v>
+      </c>
+      <c r="F22" cm="1">
+        <f t="array" ref="F22">_xll.PLACKETT.UV($C22,F$3,theta)</f>
+        <v>1.828652524625822E-2</v>
+      </c>
+      <c r="G22" cm="1">
+        <f t="array" ref="G22">_xll.PLACKETT.UV($C22,G$3,theta)</f>
+        <v>6.0464436173095923E-2</v>
+      </c>
+      <c r="H22" cm="1">
+        <f t="array" ref="H22">_xll.PLACKETT.UV($C22,H$3,theta)</f>
+        <v>0.43501073894100922</v>
+      </c>
+      <c r="I22" cm="1">
+        <f t="array" ref="I22">_xll.PLACKETT.UV($C22,I$3,theta)</f>
+        <v>15.827199689142736</v>
+      </c>
+      <c r="J22" cm="1">
+        <f t="array" ref="J22">_xll.PLACKETT.UV($C22,J$3,theta)</f>
+        <v>0.43501073894100939</v>
+      </c>
+      <c r="K22" cm="1">
+        <f t="array" ref="K22">_xll.PLACKETT.UV($C22,K$3,theta)</f>
+        <v>6.0464436173096006E-2</v>
+      </c>
+      <c r="L22" cm="1">
+        <f t="array" ref="L22">_xll.PLACKETT.UV($C22,L$3,theta)</f>
+        <v>1.8286525246258237E-2</v>
+      </c>
+      <c r="M22" cm="1">
+        <f t="array" ref="M22">_xll.PLACKETT.UV($C22,M$3,theta)</f>
+        <v>7.7707099460882639E-3</v>
+      </c>
+      <c r="N22" cm="1">
+        <f t="array" ref="N22">_xll.PLACKETT.UV($C22,N$3,theta)</f>
+        <v>3.9920119840199759E-3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="C23">
+        <v>0.6</v>
+      </c>
+      <c r="D23" cm="1">
+        <f t="array" ref="D23">_xll.PLACKETT.UV($C23,D$3,theta)</f>
+        <v>6.2312921032829172E-3</v>
+      </c>
+      <c r="E23" cm="1">
+        <f t="array" ref="E23">_xll.PLACKETT.UV($C23,E$3,theta)</f>
+        <v>1.5407183256802326E-2</v>
+      </c>
+      <c r="F23" cm="1">
+        <f t="array" ref="F23">_xll.PLACKETT.UV($C23,F$3,theta)</f>
+        <v>5.3457945533076284E-2</v>
+      </c>
+      <c r="G23" cm="1">
+        <f t="array" ref="G23">_xll.PLACKETT.UV($C23,G$3,theta)</f>
+        <v>0.40468977437845532</v>
+      </c>
+      <c r="H23" cm="1">
+        <f t="array" ref="H23">_xll.PLACKETT.UV($C23,H$3,theta)</f>
+        <v>16.153903196224309</v>
+      </c>
+      <c r="I23" cm="1">
+        <f t="array" ref="I23">_xll.PLACKETT.UV($C23,I$3,theta)</f>
+        <v>0.43501073894100939</v>
+      </c>
+      <c r="J23" cm="1">
+        <f t="array" ref="J23">_xll.PLACKETT.UV($C23,J$3,theta)</f>
+        <v>6.2786189138963375E-2</v>
+      </c>
+      <c r="K23" cm="1">
+        <f t="array" ref="K23">_xll.PLACKETT.UV($C23,K$3,theta)</f>
+        <v>1.9720488121697591E-2</v>
+      </c>
+      <c r="L23" cm="1">
+        <f t="array" ref="L23">_xll.PLACKETT.UV($C23,L$3,theta)</f>
+        <v>8.6916032918170176E-3</v>
+      </c>
+      <c r="M23" cm="1">
+        <f t="array" ref="M23">_xll.PLACKETT.UV($C23,M$3,theta)</f>
+        <v>4.6250302965488051E-3</v>
+      </c>
+      <c r="N23" cm="1">
+        <f t="array" ref="N23">_xll.PLACKETT.UV($C23,N$3,theta)</f>
+        <v>2.7740777744883365E-3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="C24">
+        <v>0.7</v>
+      </c>
+      <c r="D24" cm="1">
+        <f t="array" ref="D24">_xll.PLACKETT.UV($C24,D$3,theta)</f>
+        <v>1.105944017777386E-2</v>
+      </c>
+      <c r="E24" cm="1">
+        <f t="array" ref="E24">_xll.PLACKETT.UV($C24,E$3,theta)</f>
+        <v>4.1641495228951074E-2</v>
+      </c>
+      <c r="F24" cm="1">
+        <f t="array" ref="F24">_xll.PLACKETT.UV($C24,F$3,theta)</f>
+        <v>0.34195583529660456</v>
+      </c>
+      <c r="G24" cm="1">
+        <f t="array" ref="G24">_xll.PLACKETT.UV($C24,G$3,theta)</f>
+        <v>17.270528003950261</v>
+      </c>
+      <c r="H24" cm="1">
+        <f t="array" ref="H24">_xll.PLACKETT.UV($C24,H$3,theta)</f>
+        <v>0.40468977437845638</v>
+      </c>
+      <c r="I24" cm="1">
+        <f t="array" ref="I24">_xll.PLACKETT.UV($C24,I$3,theta)</f>
+        <v>6.0464436173096006E-2</v>
+      </c>
+      <c r="J24" cm="1">
+        <f t="array" ref="J24">_xll.PLACKETT.UV($C24,J$3,theta)</f>
+        <v>1.9720488121697591E-2</v>
+      </c>
+      <c r="K24" cm="1">
+        <f t="array" ref="K24">_xll.PLACKETT.UV($C24,K$3,theta)</f>
+        <v>8.9981094652824747E-3</v>
+      </c>
+      <c r="L24" cm="1">
+        <f t="array" ref="L24">_xll.PLACKETT.UV($C24,L$3,theta)</f>
+        <v>4.9410850590055041E-3</v>
+      </c>
+      <c r="M24" cm="1">
+        <f t="array" ref="M24">_xll.PLACKETT.UV($C24,M$3,theta)</f>
+        <v>3.0495021897984347E-3</v>
+      </c>
+      <c r="N24" cm="1">
+        <f t="array" ref="N24">_xll.PLACKETT.UV($C24,N$3,theta)</f>
+        <v>2.0390681792827863E-3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="C25">
+        <v>0.8</v>
+      </c>
+      <c r="D25" cm="1">
+        <f t="array" ref="D25">_xll.PLACKETT.UV($C25,D$3,theta)</f>
+        <v>2.4801193631847115E-2</v>
+      </c>
+      <c r="E25" cm="1">
+        <f t="array" ref="E25">_xll.PLACKETT.UV($C25,E$3,theta)</f>
+        <v>0.24232226107297336</v>
+      </c>
+      <c r="F25" cm="1">
+        <f t="array" ref="F25">_xll.PLACKETT.UV($C25,F$3,theta)</f>
+        <v>19.789534608545942</v>
+      </c>
+      <c r="G25" cm="1">
+        <f t="array" ref="G25">_xll.PLACKETT.UV($C25,G$3,theta)</f>
+        <v>0.3419558352966055</v>
+      </c>
+      <c r="H25" cm="1">
+        <f t="array" ref="H25">_xll.PLACKETT.UV($C25,H$3,theta)</f>
+        <v>5.3457945533076208E-2</v>
+      </c>
+      <c r="I25" cm="1">
+        <f t="array" ref="I25">_xll.PLACKETT.UV($C25,I$3,theta)</f>
+        <v>1.8286525246258237E-2</v>
+      </c>
+      <c r="J25" cm="1">
+        <f t="array" ref="J25">_xll.PLACKETT.UV($C25,J$3,theta)</f>
+        <v>8.6916032918170176E-3</v>
+      </c>
+      <c r="K25" cm="1">
+        <f t="array" ref="K25">_xll.PLACKETT.UV($C25,K$3,theta)</f>
+        <v>4.9410850590055041E-3</v>
+      </c>
+      <c r="L25" cm="1">
+        <f t="array" ref="L25">_xll.PLACKETT.UV($C25,L$3,theta)</f>
+        <v>3.1412492431216045E-3</v>
+      </c>
+      <c r="M25" cm="1">
+        <f t="array" ref="M25">_xll.PLACKETT.UV($C25,M$3,theta)</f>
+        <v>2.1548932066352494E-3</v>
+      </c>
+      <c r="N25" cm="1">
+        <f t="array" ref="N25">_xll.PLACKETT.UV($C25,N$3,theta)</f>
+        <v>1.5617190428711244E-3</v>
+      </c>
+    </row>
+    <row r="26" spans="3:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="C26">
+        <v>0.9</v>
+      </c>
+      <c r="D26" cm="1">
+        <f t="array" ref="D26">_xll.PLACKETT.UV($C26,D$3,theta)</f>
+        <v>9.8224011645438827E-2</v>
+      </c>
+      <c r="E26" cm="1">
+        <f t="array" ref="E26">_xll.PLACKETT.UV($C26,E$3,theta)</f>
+        <v>26.401926844269422</v>
+      </c>
+      <c r="F26" cm="1">
+        <f t="array" ref="F26">_xll.PLACKETT.UV($C26,F$3,theta)</f>
+        <v>0.24232226107297336</v>
+      </c>
+      <c r="G26" cm="1">
+        <f t="array" ref="G26">_xll.PLACKETT.UV($C26,G$3,theta)</f>
+        <v>4.1641495228951206E-2</v>
+      </c>
+      <c r="H26" cm="1">
+        <f t="array" ref="H26">_xll.PLACKETT.UV($C26,H$3,theta)</f>
+        <v>1.5407183256802345E-2</v>
+      </c>
+      <c r="I26" cm="1">
+        <f t="array" ref="I26">_xll.PLACKETT.UV($C26,I$3,theta)</f>
+        <v>7.7707099460882639E-3</v>
+      </c>
+      <c r="J26" cm="1">
+        <f t="array" ref="J26">_xll.PLACKETT.UV($C26,J$3,theta)</f>
+        <v>4.6250302965488051E-3</v>
+      </c>
+      <c r="K26" cm="1">
+        <f t="array" ref="K26">_xll.PLACKETT.UV($C26,K$3,theta)</f>
+        <v>3.0495021897984347E-3</v>
+      </c>
+      <c r="L26" cm="1">
+        <f t="array" ref="L26">_xll.PLACKETT.UV($C26,L$3,theta)</f>
+        <v>2.1548932066352494E-3</v>
+      </c>
+      <c r="M26" cm="1">
+        <f t="array" ref="M26">_xll.PLACKETT.UV($C26,M$3,theta)</f>
+        <v>1.6005633972407806E-3</v>
+      </c>
+      <c r="N26" cm="1">
+        <f t="array" ref="N26">_xll.PLACKETT.UV($C26,N$3,theta)</f>
+        <v>1.2342935985300359E-3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="C27">
+        <v>1</v>
+      </c>
+      <c r="D27" cm="1">
+        <f t="array" ref="D27">_xll.PLACKETT.UV($C27,D$3,theta)</f>
+        <v>999.99999999999829</v>
+      </c>
+      <c r="E27" cm="1">
+        <f t="array" ref="E27">_xll.PLACKETT.UV($C27,E$3,theta)</f>
+        <v>9.8224011645438758E-2</v>
+      </c>
+      <c r="F27" cm="1">
+        <f t="array" ref="F27">_xll.PLACKETT.UV($C27,F$3,theta)</f>
+        <v>2.4801193631847174E-2</v>
+      </c>
+      <c r="G27" cm="1">
+        <f t="array" ref="G27">_xll.PLACKETT.UV($C27,G$3,theta)</f>
+        <v>1.1059440177773869E-2</v>
+      </c>
+      <c r="H27" cm="1">
+        <f t="array" ref="H27">_xll.PLACKETT.UV($C27,H$3,theta)</f>
+        <v>6.2312921032829285E-3</v>
+      </c>
+      <c r="I27" cm="1">
+        <f t="array" ref="I27">_xll.PLACKETT.UV($C27,I$3,theta)</f>
+        <v>3.9920119840199759E-3</v>
+      </c>
+      <c r="J27" cm="1">
+        <f t="array" ref="J27">_xll.PLACKETT.UV($C27,J$3,theta)</f>
+        <v>2.7740777744883365E-3</v>
+      </c>
+      <c r="K27" cm="1">
+        <f t="array" ref="K27">_xll.PLACKETT.UV($C27,K$3,theta)</f>
+        <v>2.0390681792827863E-3</v>
+      </c>
+      <c r="L27" cm="1">
+        <f t="array" ref="L27">_xll.PLACKETT.UV($C27,L$3,theta)</f>
+        <v>1.5617190428711244E-3</v>
+      </c>
+      <c r="M27" cm="1">
+        <f t="array" ref="M27">_xll.PLACKETT.UV($C27,M$3,theta)</f>
+        <v>1.2342935985300359E-3</v>
+      </c>
+      <c r="N27" cm="1">
+        <f t="array" ref="N27">_xll.PLACKETT.UV($C27,N$3,theta)</f>
+        <v>1E-3</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>